--- a/data/WGC/Test_Report_WGC.xlsx
+++ b/data/WGC/Test_Report_WGC.xlsx
@@ -478,6 +478,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/data/WGC/Test_Report_WGC.xlsx
+++ b/data/WGC/Test_Report_WGC.xlsx
@@ -31,25 +31,22 @@
     <t>Result</t>
   </si>
   <si>
-    <t>13/05/2026, 15:14:30</t>
-  </si>
-  <si>
-    <t>wgctest01_tkw@mailinator.com</t>
-  </si>
-  <si>
-    <t>Somchai</t>
-  </si>
-  <si>
-    <t>Jaidee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">page.waitForURL: Timeout 15000ms exceeded.
-=========================== logs ===========================
-waiting for navigation until "load"
-============================================================</t>
-  </si>
-  <si>
-    <t>FAIL</t>
+    <t>19/05/2026, 14:32:18</t>
+  </si>
+  <si>
+    <t>wgctest01_5bq@mailinator.com</t>
+  </si>
+  <si>
+    <t>Charlie</t>
+  </si>
+  <si>
+    <t>Bayer</t>
+  </si>
+  <si>
+    <t>Success</t>
+  </si>
+  <si>
+    <t>PASS</t>
   </si>
 </sst>
 </file>
